--- a/Project/outputs/tables/table_lstm_metrics_h5.xlsx
+++ b/Project/outputs/tables/table_lstm_metrics_h5.xlsx
@@ -482,19 +482,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003554560709744692</v>
+        <v>0.003407639218494296</v>
       </c>
       <c r="C2" t="n">
-        <v>0.03558534383773804</v>
+        <v>0.03712859004735947</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05962013678066071</v>
+        <v>0.05837498795284069</v>
       </c>
       <c r="E2" t="n">
-        <v>23.02755737304688</v>
+        <v>25.07109260559082</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4564393939393939</v>
+        <v>0.4522058823529412</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -513,23 +513,23 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>STOXX600</t>
+          <t>DAX</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001673483406193554</v>
+        <v>0.001925672055222094</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02603845857083797</v>
+        <v>0.02877053990960121</v>
       </c>
       <c r="D3" t="n">
-        <v>0.04090823152121776</v>
+        <v>0.04388248004867198</v>
       </c>
       <c r="E3" t="n">
-        <v>17.99226951599121</v>
+        <v>17.29781532287598</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4659090909090909</v>
+        <v>0.5055147058823529</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -548,23 +548,23 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FTSE100</t>
+          <t>CAC40</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.002013701945543289</v>
+        <v>0.002382630249485373</v>
       </c>
       <c r="C4" t="n">
-        <v>0.02933438494801521</v>
+        <v>0.03408149257302284</v>
       </c>
       <c r="D4" t="n">
-        <v>0.04487429047398175</v>
+        <v>0.04881219365573907</v>
       </c>
       <c r="E4" t="n">
-        <v>17.73147773742676</v>
+        <v>21.62223243713379</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4924242424242424</v>
+        <v>0.4669117647058824</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -583,23 +583,23 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DAX</t>
+          <t>FTSE100</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.001823024125769734</v>
+        <v>0.001590155879966915</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02775490283966064</v>
+        <v>0.02777438797056675</v>
       </c>
       <c r="D5" t="n">
-        <v>0.04269688660511132</v>
+        <v>0.03987675864418916</v>
       </c>
       <c r="E5" t="n">
-        <v>15.81237316131592</v>
+        <v>18.17229461669922</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4734848484848485</v>
+        <v>0.4944852941176471</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -622,19 +622,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001533059403300285</v>
+        <v>0.001255129696801305</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02643081545829773</v>
+        <v>0.02432595752179623</v>
       </c>
       <c r="D6" t="n">
-        <v>0.03915430248772522</v>
+        <v>0.03542780965288857</v>
       </c>
       <c r="E6" t="n">
-        <v>13.14613628387451</v>
+        <v>12.85302639007568</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5056818181818182</v>
+        <v>0.4944852941176471</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -653,23 +653,23 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HangSeng</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001346495235338807</v>
+        <v>0.001869102357886732</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02609831839799881</v>
+        <v>0.02629019133746624</v>
       </c>
       <c r="D7" t="n">
-        <v>0.03669462134071978</v>
+        <v>0.04323311644892988</v>
       </c>
       <c r="E7" t="n">
-        <v>13.43930244445801</v>
+        <v>13.72501277923584</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4734848484848485</v>
+        <v>0.4632352941176471</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -688,23 +688,23 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MSCI_EM</t>
+          <t>HangSeng</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.00308877625502646</v>
+        <v>0.001798323704861104</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03834932297468185</v>
+        <v>0.03018422238528728</v>
       </c>
       <c r="D8" t="n">
-        <v>0.05557676002634968</v>
+        <v>0.04240664694197249</v>
       </c>
       <c r="E8" t="n">
-        <v>19.60467910766602</v>
+        <v>15.53729438781738</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4659090909090909</v>
+        <v>0.5018382352941176</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -723,23 +723,23 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CSI300</t>
+          <t>SSE</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.001105546136386693</v>
+        <v>0.001416910672560334</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0222441740334034</v>
+        <v>0.02856522984802723</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03324975392971642</v>
+        <v>0.03764187392466446</v>
       </c>
       <c r="E9" t="n">
-        <v>11.57380199432373</v>
+        <v>19.44024276733398</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4981060606060606</v>
+        <v>0.46875</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -762,19 +762,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.002017330902162939</v>
+        <v>0.001955695479409769</v>
       </c>
       <c r="C10" t="n">
-        <v>0.02897946513257921</v>
+        <v>0.02964007644914091</v>
       </c>
       <c r="D10" t="n">
-        <v>0.04409687289568533</v>
+        <v>0.04370698340873704</v>
       </c>
       <c r="E10" t="n">
-        <v>16.54094886779785</v>
+        <v>17.96487808227539</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4789299242424243</v>
+        <v>0.4809283088235294</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -797,19 +797,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.001010210020467639</v>
+        <v>0.001529387547634542</v>
       </c>
       <c r="C11" t="n">
-        <v>0.01981787756085396</v>
+        <v>0.02617543563246727</v>
       </c>
       <c r="D11" t="n">
-        <v>0.03178380122747496</v>
+        <v>0.03910738482223711</v>
       </c>
       <c r="E11" t="n">
-        <v>12.87082290649414</v>
+        <v>14.98669242858887</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.5177398160315374</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -828,23 +828,23 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>STOXX600</t>
+          <t>DAX</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.0007654430228285491</v>
+        <v>0.001040325034409761</v>
       </c>
       <c r="C12" t="n">
-        <v>0.01771120354533195</v>
+        <v>0.02299276925623417</v>
       </c>
       <c r="D12" t="n">
-        <v>0.02766664097480121</v>
+        <v>0.03225407004410082</v>
       </c>
       <c r="E12" t="n">
-        <v>14.73204612731934</v>
+        <v>15.83049297332764</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4799465240641711</v>
+        <v>0.4848883048620237</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -863,23 +863,23 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FTSE100</t>
+          <t>CAC40</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.001208450878039002</v>
+        <v>0.001072931452654302</v>
       </c>
       <c r="C13" t="n">
-        <v>0.02562239021062851</v>
+        <v>0.0248786062002182</v>
       </c>
       <c r="D13" t="n">
-        <v>0.03476278006775353</v>
+        <v>0.0327556323806197</v>
       </c>
       <c r="E13" t="n">
-        <v>26.92871475219727</v>
+        <v>18.25946426391602</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4986631016042781</v>
+        <v>0.4888304862023653</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -898,23 +898,23 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DAX</t>
+          <t>FTSE100</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.0008545069140382111</v>
+        <v>0.001318743219599128</v>
       </c>
       <c r="C14" t="n">
-        <v>0.01906365528702736</v>
+        <v>0.02721103839576244</v>
       </c>
       <c r="D14" t="n">
-        <v>0.02923195022639118</v>
+        <v>0.03631450425930564</v>
       </c>
       <c r="E14" t="n">
-        <v>13.52900409698486</v>
+        <v>28.83820152282715</v>
       </c>
       <c r="F14" t="n">
-        <v>0.482620320855615</v>
+        <v>0.507227332457293</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -937,19 +937,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.003607770893722773</v>
+        <v>0.003696086117997766</v>
       </c>
       <c r="C15" t="n">
-        <v>0.03090811520814896</v>
+        <v>0.03158074989914894</v>
       </c>
       <c r="D15" t="n">
-        <v>0.06006472253929733</v>
+        <v>0.06079544487868944</v>
       </c>
       <c r="E15" t="n">
-        <v>14.21150588989258</v>
+        <v>14.27485179901123</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5280748663101604</v>
+        <v>0.5321944809461235</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -968,23 +968,23 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>HangSeng</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.002698538359254599</v>
+        <v>0.001808058703318238</v>
       </c>
       <c r="C16" t="n">
-        <v>0.02918641641736031</v>
+        <v>0.02712426707148552</v>
       </c>
       <c r="D16" t="n">
-        <v>0.05194745767845236</v>
+        <v>0.04252127353829185</v>
       </c>
       <c r="E16" t="n">
-        <v>11.73128223419189</v>
+        <v>15.2155294418335</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5147058823529411</v>
+        <v>0.5466491458607096</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1003,23 +1003,23 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MSCI_EM</t>
+          <t>HangSeng</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.001920364913530648</v>
+        <v>0.003125775838270783</v>
       </c>
       <c r="C17" t="n">
-        <v>0.03405671939253807</v>
+        <v>0.03575648367404938</v>
       </c>
       <c r="D17" t="n">
-        <v>0.04382196838950354</v>
+        <v>0.05590863831529778</v>
       </c>
       <c r="E17" t="n">
-        <v>22.29665946960449</v>
+        <v>14.53646087646484</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4598930481283423</v>
+        <v>0.5348226018396847</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1038,23 +1038,23 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CSI300</t>
+          <t>SSE</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.001311659463681281</v>
+        <v>0.002293025376275182</v>
       </c>
       <c r="C18" t="n">
-        <v>0.02087258920073509</v>
+        <v>0.03617284074425697</v>
       </c>
       <c r="D18" t="n">
-        <v>0.03621683950431457</v>
+        <v>0.04788554454399763</v>
       </c>
       <c r="E18" t="n">
-        <v>14.78590679168701</v>
+        <v>29.64866256713867</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5026737967914439</v>
+        <v>0.4717477003942182</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1077,19 +1077,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.001672118058195338</v>
+        <v>0.001985541661269963</v>
       </c>
       <c r="C19" t="n">
-        <v>0.02465487085282803</v>
+        <v>0.02898652385920286</v>
       </c>
       <c r="D19" t="n">
-        <v>0.03943702007599859</v>
+        <v>0.0434428115978175</v>
       </c>
       <c r="E19" t="n">
-        <v>16.3857421875</v>
+        <v>18.94879531860352</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5015040106951871</v>
+        <v>0.5105124835742444</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
